--- a/data/trans_bre/P19C03-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P19C03-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,54; 3,12</t>
+          <t>-9,79; 3,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,64; 2,75</t>
+          <t>-10,97; 2,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,79; 2,79</t>
+          <t>-10,74; 2,76</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-15,83; 4,05</t>
+          <t>-15,31; 5,73</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-25,82; 10,09</t>
+          <t>-24,65; 12,31</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-29,03; 8,9</t>
+          <t>-29,79; 8,37</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-33,58; 10,91</t>
+          <t>-32,3; 11,14</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-57,16; 27,15</t>
+          <t>-55,53; 36,67</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,12; 5,35</t>
+          <t>-7,47; 4,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,93; 5,49</t>
+          <t>-6,35; 5,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-9,32; 2,1</t>
+          <t>-9,08; 2,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-14,12; 0,84</t>
+          <t>-15,46; 0,75</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-14,37; 14,27</t>
+          <t>-17,52; 13,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-16,1; 17,44</t>
+          <t>-17,02; 16,59</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-25,37; 6,64</t>
+          <t>-25,29; 7,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-53,62; 3,65</t>
+          <t>-57,06; 3,04</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,81; 4,37</t>
+          <t>-7,12; 5,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 6,97</t>
+          <t>-3,7; 7,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,27; 1,86</t>
+          <t>-9,2; 2,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,12; 3,08</t>
+          <t>-5,8; 3,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-18,67; 12,12</t>
+          <t>-17,18; 14,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-10,42; 23,51</t>
+          <t>-9,89; 25,74</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-25,31; 5,59</t>
+          <t>-25,08; 7,42</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-24,31; 15,91</t>
+          <t>-22,52; 17,67</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,71; 5,91</t>
+          <t>-6,59; 6,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,48; 3,36</t>
+          <t>-9,16; 2,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 7,14</t>
+          <t>-4,59; 6,91</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,11; 24,53</t>
+          <t>-0,87; 23,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-17,21; 19,37</t>
+          <t>-16,92; 20,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-22,98; 11,27</t>
+          <t>-25,05; 9,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-13,69; 29,2</t>
+          <t>-14,86; 27,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 301,17</t>
+          <t>-4,84; 262,95</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,48; 16,55</t>
+          <t>2,56; 16,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 8,84</t>
+          <t>-6,16; 8,22</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 10,76</t>
+          <t>-2,48; 10,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 5,73</t>
+          <t>-2,71; 5,82</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,09; 93,2</t>
+          <t>11,14; 101,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-16,59; 33,49</t>
+          <t>-18,51; 30,24</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-9,48; 62,84</t>
+          <t>-10,46; 57,38</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-11,44; 34,4</t>
+          <t>-12,47; 35,41</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,04; 14,82</t>
+          <t>1,81; 15,11</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 10,59</t>
+          <t>-2,43; 10,96</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 9,79</t>
+          <t>-4,24; 10,29</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-11,24; 3,98</t>
+          <t>-11,43; 4,19</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11,0; 156,87</t>
+          <t>10,66; 160,07</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-12,79; 87,59</t>
+          <t>-12,6; 92,62</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-15,47; 63,8</t>
+          <t>-19,27; 67,96</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-74,26; 31,61</t>
+          <t>-73,61; 34,82</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 4,8</t>
+          <t>-5,77; 4,96</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,53; 3,74</t>
+          <t>-6,25; 3,8</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 9,45</t>
+          <t>-4,29; 9,16</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 2,95</t>
+          <t>-3,63; 2,9</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-64,27; 186,47</t>
+          <t>-64,2; 215,83</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-57,62; 81,26</t>
+          <t>-56,31; 80,98</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-39,49; 136,5</t>
+          <t>-34,95; 131,13</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-34,54; 49,06</t>
+          <t>-35,83; 48,4</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 2,75</t>
+          <t>-2,58; 2,75</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 1,21</t>
+          <t>-3,5; 1,52</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 1,14</t>
+          <t>-3,57; 1,15</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 3,76</t>
+          <t>-3,8; 4,09</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-7,47; 9,06</t>
+          <t>-7,8; 9,03</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-11,76; 4,17</t>
+          <t>-11,21; 5,28</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-13,26; 4,17</t>
+          <t>-12,49; 4,33</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-19,72; 24,24</t>
+          <t>-19,68; 25,83</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P19C03-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P19C03-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-4,83</t>
+          <t>-6,44</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-22,65%</t>
+          <t>-28,27%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,79; 3,77</t>
+          <t>-9,99; 3,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,97; 2,59</t>
+          <t>-10,96; 2,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,74; 2,76</t>
+          <t>-10,88; 2,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-15,31; 5,73</t>
+          <t>-15,77; 3,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-24,65; 12,31</t>
+          <t>-25,73; 10,26</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-29,79; 8,37</t>
+          <t>-29,42; 9,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-32,3; 11,14</t>
+          <t>-32,72; 10,57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-55,53; 36,67</t>
+          <t>-56,76; 23,01</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-5,93</t>
+          <t>-1,98</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-25,86%</t>
+          <t>-8,98%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,47; 4,97</t>
+          <t>-5,98; 5,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,35; 5,18</t>
+          <t>-5,84; 5,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-9,08; 2,27</t>
+          <t>-9,9; 1,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-15,46; 0,75</t>
+          <t>-8,33; 4,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-17,52; 13,49</t>
+          <t>-13,8; 15,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-17,02; 16,59</t>
+          <t>-15,75; 16,57</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-25,29; 7,71</t>
+          <t>-27,11; 5,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-57,06; 3,04</t>
+          <t>-32,7; 24,55</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-1,31</t>
+          <t>0,36</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-5,84%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,12; 5,08</t>
+          <t>-6,92; 4,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 7,73</t>
+          <t>-3,29; 7,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,2; 2,22</t>
+          <t>-9,23; 2,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,8; 3,56</t>
+          <t>-4,32; 4,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-17,18; 14,57</t>
+          <t>-17,07; 11,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,89; 25,74</t>
+          <t>-9,08; 23,31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-25,08; 7,42</t>
+          <t>-25,35; 6,33</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-22,52; 17,67</t>
+          <t>-18,22; 24,59</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8,53</t>
+          <t>-1,11</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>-5,03%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,59; 6,41</t>
+          <t>-6,61; 6,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-9,16; 2,92</t>
+          <t>-8,61; 2,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 6,91</t>
+          <t>-4,85; 6,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 23,28</t>
+          <t>-5,07; 3,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-16,92; 20,75</t>
+          <t>-16,77; 21,43</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-25,05; 9,92</t>
+          <t>-23,94; 9,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-14,86; 27,79</t>
+          <t>-15,6; 26,43</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 262,95</t>
+          <t>-20,61; 15,55</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,58</t>
+          <t>2,31</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>12,46%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,56; 16,51</t>
+          <t>2,91; 16,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 8,22</t>
+          <t>-5,73; 8,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 10,15</t>
+          <t>-2,23; 10,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 5,82</t>
+          <t>-1,73; 6,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,14; 101,07</t>
+          <t>12,25; 97,56</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-18,51; 30,24</t>
+          <t>-16,79; 31,86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-10,46; 57,38</t>
+          <t>-9,84; 58,89</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-12,47; 35,41</t>
+          <t>-8,31; 38,66</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-2,63</t>
+          <t>2,85</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-19,91%</t>
+          <t>21,91%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,81; 15,11</t>
+          <t>1,76; 14,66</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 10,96</t>
+          <t>-2,67; 10,84</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 10,29</t>
+          <t>-3,78; 10,64</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-11,43; 4,19</t>
+          <t>-1,42; 6,59</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10,66; 160,07</t>
+          <t>8,25; 156,68</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-12,6; 92,62</t>
+          <t>-13,07; 90,1</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-19,27; 67,96</t>
+          <t>-16,16; 70,25</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-73,61; 34,82</t>
+          <t>-8,88; 62,18</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0,09</t>
+          <t>-0,25</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-1,11%</t>
+          <t>-2,99%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 4,96</t>
+          <t>-5,65; 4,79</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 3,8</t>
+          <t>-7,13; 3,43</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 9,16</t>
+          <t>-4,59; 8,29</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 2,9</t>
+          <t>-3,66; 2,53</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-64,2; 215,83</t>
+          <t>-67,09; 181,39</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-56,31; 80,98</t>
+          <t>-58,6; 72,73</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-34,95; 131,13</t>
+          <t>-36,7; 117,61</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-35,83; 48,4</t>
+          <t>-36,58; 39,89</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-0,5</t>
+          <t>-0,8</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-2,79%</t>
+          <t>-4,16%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 2,75</t>
+          <t>-2,38; 2,75</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 1,52</t>
+          <t>-3,67; 1,39</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 1,15</t>
+          <t>-3,68; 0,93</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 4,09</t>
+          <t>-2,78; 1,0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-7,8; 9,03</t>
+          <t>-7,27; 9,11</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-11,21; 5,28</t>
+          <t>-11,64; 4,87</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-12,49; 4,33</t>
+          <t>-12,85; 3,53</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-19,68; 25,83</t>
+          <t>-13,84; 5,73</t>
         </is>
       </c>
     </row>
